--- a/doc/imap-lo_pipline_change_summary.xlsx
+++ b/doc/imap-lo_pipline_change_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fle4/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nschwadron/Computer/IMAP_Lo/quickpipeline/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C12521-1399-1743-8C7D-E6BCFF592BCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB6760E-5A7B-974F-B00A-2D975C15965B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3320" windowWidth="28040" windowHeight="17180" xr2:uid="{A0393EFD-59B7-9B4C-9B9E-5A20723682EB}"/>
+    <workbookView xWindow="12640" yWindow="500" windowWidth="28040" windowHeight="17180" xr2:uid="{A0393EFD-59B7-9B4C-9B9E-5A20723682EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>change No.</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>imap-lo_pipline_gt_001.pdf (GoodTimes_presentation)/ imap-lo_pipline_gt_002.docx</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>1S04</t>
   </si>
 </sst>
 </file>
@@ -458,66 +464,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{133B55E6-89D2-664D-83C2-3B47FC53490F}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="54.6640625" customWidth="1"/>
-    <col min="6" max="6" width="20.1640625" customWidth="1"/>
-    <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="40.1640625" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="54.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" customWidth="1"/>
+    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
